--- a/neics/NEICS_Data_Requirements.xlsx
+++ b/neics/NEICS_Data_Requirements.xlsx
@@ -576,7 +576,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>• 'Provider register' lists every entity that must supply data. Filter the 'Source bucket' column to separate EXTERNAL ministries/authorities from INTERNAL NSO/PSA (MPC) sources.</t>
+          <t>• 'Provider register' lists every entity that must supply data. Filter the 'Source bucket' column to separate EXTERNAL ministries/authorities from INTERNAL NPC (Statistics &amp; Surveys) sources.</t>
         </is>
       </c>
     </row>
@@ -638,14 +638,14 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Terminology note — 'MPC'</t>
+          <t>Terminology note — 'NPC'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>• 'MPC' in the request has been interpreted as the internal statistical production centre (NSO / PSA) that operates NEICS. Internal sources are tagged 'INTERNAL — NSO/PSA (MPC)'. Please confirm if a different body is meant.</t>
+          <t>• Internal sources are the National Statistics Office functions under the NPC — including the Economic Surveys / large-case profiling department. They are tagged 'INTERNAL — NPC (Statistics &amp; Surveys)'.</t>
         </is>
       </c>
     </row>
@@ -1644,17 +1644,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA — Economic surveys &amp; large-case profiling</t>
+          <t>NPC — National Statistics Office: Economic Surveys &amp; Large-Case Profiling</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Internal — NSO/PSA</t>
+          <t>Internal — NPC</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA — Statistical Business Register (SBR)</t>
+          <t>NPC — National Statistics Office: Statistical Business Register (SBR)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Internal — NSO/PSA</t>
+          <t>Internal — NPC</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA — Classification portal (manual / committee)</t>
+          <t>NPC — National Statistics Office: Classification portal (manual / committee)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Internal — NSO/PSA</t>
+          <t>Internal — NPC</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-17)</t>
+          <t>NPC (P-17)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-17)</t>
+          <t>NPC (P-17)</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-17)</t>
+          <t>NPC (P-17)</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-17)</t>
+          <t>NPC (P-17)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-17)</t>
+          <t>NPC (P-17)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA (P-16)</t>
+          <t>NPC (P-16)</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>INTERNAL — NSO/PSA (MPC)</t>
+          <t>INTERNAL — NPC (Statistics &amp; Surveys)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>NSO / PSA</t>
+          <t>NPC — NSO</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>NPC Council</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>NSO / PSA</t>
+          <t>NPC — NSO</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
